--- a/Vanadium_Cij_finite_strain_all_equations_GlobalMin_backup.xlsx
+++ b/Vanadium_Cij_finite_strain_all_equations_GlobalMin_backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bgulick\Downloads\vCIJ_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBCDB20-0A51-47FD-A137-94EB72E63BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE896924-5BA0-47EA-8DC8-6C7CA9B40FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{5F35EC34-C410-40C3-9DB6-F447C7BA1DCF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5F35EC34-C410-40C3-9DB6-F447C7BA1DCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="5" r:id="rId1"/>
@@ -1190,13 +1190,13 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9036,6 +9036,7 @@
       <c r="AW1" s="75" t="s">
         <v>146</v>
       </c>
+      <c r="AX1" s="7"/>
       <c r="AY1" s="3"/>
       <c r="AZ1" s="65"/>
       <c r="BA1" s="1" t="s">
@@ -9329,6 +9330,7 @@
         <f t="shared" ref="AW2:AW23" si="14">AO2-A2</f>
         <v>0</v>
       </c>
+      <c r="AX2" s="7"/>
       <c r="AY2" s="17"/>
       <c r="AZ2" s="65"/>
       <c r="BA2" s="12">
@@ -9676,6 +9678,7 @@
         <f t="shared" si="14"/>
         <v>9.8789332047474199E-3</v>
       </c>
+      <c r="AX3" s="7"/>
       <c r="AY3" s="17"/>
       <c r="AZ3" s="65"/>
       <c r="BA3" s="12">
@@ -10016,6 +10019,7 @@
         <f t="shared" si="14"/>
         <v>6.8015769978871488E-2</v>
       </c>
+      <c r="AX4" s="7"/>
       <c r="AY4" s="17"/>
       <c r="AZ4" s="65"/>
       <c r="BA4" s="12">
@@ -10356,6 +10360,7 @@
         <f t="shared" si="14"/>
         <v>9.5863851594324423E-2</v>
       </c>
+      <c r="AX5" s="7"/>
       <c r="AY5" s="17"/>
       <c r="AZ5" s="65"/>
       <c r="BA5" s="12">
@@ -10696,6 +10701,7 @@
         <f t="shared" si="14"/>
         <v>0.12343852086956852</v>
       </c>
+      <c r="AX6" s="7"/>
       <c r="AY6" s="31"/>
       <c r="AZ6" s="65"/>
       <c r="BA6" s="55">
@@ -11036,6 +11042,7 @@
         <f t="shared" si="14"/>
         <v>0.1499886488321609</v>
       </c>
+      <c r="AX7" s="7"/>
       <c r="AY7" s="17"/>
       <c r="AZ7" s="65"/>
       <c r="BA7" s="12">
@@ -11376,6 +11383,7 @@
         <f t="shared" si="14"/>
         <v>0.16721446142081131</v>
       </c>
+      <c r="AX8" s="7"/>
       <c r="AY8" s="17"/>
       <c r="AZ8" s="65"/>
       <c r="BA8" s="12">
@@ -11716,6 +11724,7 @@
         <f t="shared" si="14"/>
         <v>0.1831042740023241</v>
       </c>
+      <c r="AX9" s="7"/>
       <c r="AY9" s="17"/>
       <c r="AZ9" s="65"/>
       <c r="BA9" s="12">
@@ -12056,6 +12065,7 @@
         <f t="shared" si="14"/>
         <v>0.20296301416316442</v>
       </c>
+      <c r="AX10" s="7"/>
       <c r="AY10" s="17"/>
       <c r="AZ10" s="65"/>
       <c r="BA10" s="12">
@@ -12396,6 +12406,7 @@
         <f t="shared" si="14"/>
         <v>0.21880026532250518</v>
       </c>
+      <c r="AX11" s="7"/>
       <c r="AY11" s="17"/>
       <c r="AZ11" s="65"/>
       <c r="BA11" s="12">
@@ -12736,6 +12747,7 @@
         <f t="shared" si="14"/>
         <v>0.2314109659862309</v>
       </c>
+      <c r="AX12" s="7"/>
       <c r="AY12" s="17"/>
       <c r="AZ12" s="65"/>
       <c r="BA12" s="12">
@@ -13076,6 +13088,7 @@
         <f t="shared" si="14"/>
         <v>0.24684713979537065</v>
       </c>
+      <c r="AX13" s="7"/>
       <c r="AY13" s="17"/>
       <c r="AZ13" s="65"/>
       <c r="BA13" s="12">
@@ -13416,6 +13429,7 @@
         <f t="shared" si="14"/>
         <v>0.25987433984527897</v>
       </c>
+      <c r="AX14" s="7"/>
       <c r="AY14" s="17"/>
       <c r="AZ14" s="65"/>
       <c r="BA14" s="12">
@@ -13756,6 +13770,7 @@
         <f t="shared" si="14"/>
         <v>0.26916425819585754</v>
       </c>
+      <c r="AX15" s="7"/>
       <c r="AY15" s="17"/>
       <c r="AZ15" s="65"/>
       <c r="BA15" s="12">
@@ -14096,6 +14111,7 @@
         <f t="shared" si="14"/>
         <v>0.28167782263634322</v>
       </c>
+      <c r="AX16" s="7"/>
       <c r="AY16" s="43"/>
       <c r="AZ16" s="65"/>
       <c r="BA16" s="55">
@@ -14436,6 +14452,7 @@
         <f t="shared" si="14"/>
         <v>0.29302580959065772</v>
       </c>
+      <c r="AX17" s="7"/>
       <c r="AY17" s="17"/>
       <c r="AZ17" s="65"/>
       <c r="BA17" s="12">
@@ -14776,6 +14793,7 @@
         <f t="shared" si="14"/>
         <v>0.29922911823597254</v>
       </c>
+      <c r="AX18" s="7"/>
       <c r="AY18" s="17"/>
       <c r="AZ18" s="65"/>
       <c r="BA18" s="12">
@@ -15116,6 +15134,7 @@
         <f t="shared" si="14"/>
         <v>0.3034644352338578</v>
       </c>
+      <c r="AX19" s="7"/>
       <c r="AY19" s="17"/>
       <c r="AZ19" s="65"/>
       <c r="BA19" s="12">
@@ -15456,6 +15475,7 @@
         <f t="shared" si="14"/>
         <v>0.31095292728583424</v>
       </c>
+      <c r="AX20" s="7"/>
       <c r="AY20" s="17"/>
       <c r="AZ20" s="65"/>
       <c r="BA20" s="12">
@@ -15796,6 +15816,7 @@
         <f t="shared" si="14"/>
         <v>0.32033730761283685</v>
       </c>
+      <c r="AX21" s="7"/>
       <c r="AY21" s="17"/>
       <c r="AZ21" s="65"/>
       <c r="BA21" s="12">
@@ -16136,6 +16157,7 @@
         <f t="shared" si="14"/>
         <v>0.32436974513531247</v>
       </c>
+      <c r="AX22" s="7"/>
       <c r="AY22" s="17"/>
       <c r="AZ22" s="65"/>
       <c r="BA22" s="12">
@@ -16471,6 +16493,7 @@
         <f t="shared" si="14"/>
         <v>0.32674405933731521</v>
       </c>
+      <c r="AX23" s="7"/>
       <c r="AY23" s="17"/>
       <c r="AZ23" s="65"/>
       <c r="BA23" s="12">
@@ -17628,16 +17651,16 @@
         <f t="shared" si="71"/>
         <v>-1.8871371293862869E-2</v>
       </c>
-      <c r="BJ50" s="104" t="s">
+      <c r="BJ50" s="105" t="s">
         <v>135</v>
       </c>
-      <c r="BK50" s="105"/>
-      <c r="BL50" s="105"/>
-      <c r="BQ50" s="104" t="s">
+      <c r="BK50" s="106"/>
+      <c r="BL50" s="106"/>
+      <c r="BQ50" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="BR50" s="105"/>
-      <c r="BS50" s="105"/>
+      <c r="BR50" s="106"/>
+      <c r="BS50" s="106"/>
       <c r="BV50" s="21"/>
       <c r="BZ50" s="14"/>
       <c r="CA50" s="14"/>
@@ -17977,16 +18000,16 @@
       </c>
     </row>
     <row r="64" spans="1:79" x14ac:dyDescent="0.2">
-      <c r="BJ64" s="104" t="s">
+      <c r="BJ64" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="BK64" s="105"/>
-      <c r="BL64" s="105"/>
-      <c r="BP64" s="104" t="s">
+      <c r="BK64" s="106"/>
+      <c r="BL64" s="106"/>
+      <c r="BP64" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="BQ64" s="105"/>
-      <c r="BR64" s="105"/>
+      <c r="BQ64" s="106"/>
+      <c r="BR64" s="106"/>
     </row>
     <row r="65" spans="61:73" ht="15.75" x14ac:dyDescent="0.25">
       <c r="BI65" s="46" t="s">
@@ -49119,7 +49142,7 @@
       <c r="N22" t="s">
         <v>200</v>
       </c>
-      <c r="O22" s="106" t="s">
+      <c r="O22" s="104" t="s">
         <v>203</v>
       </c>
     </row>
